--- a/__chapter-3/hw3/logistics.xlsx
+++ b/__chapter-3/hw3/logistics.xlsx
@@ -83,7 +83,10 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -91,11 +94,20 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
@@ -419,4362 +431,4668 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:S101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.43359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="2" min="2" max="2"/>
-    <col width="10.4" customWidth="1" style="2" min="3" max="3"/>
-    <col width="9.630000000000001" customWidth="1" style="2" min="4" max="4"/>
-    <col width="10.06" customWidth="1" style="2" min="5" max="5"/>
-    <col width="16.31" customWidth="1" style="2" min="6" max="6"/>
-    <col width="16.14" customWidth="1" style="2" min="7" max="7"/>
-    <col width="19.78" customWidth="1" style="2" min="8" max="8"/>
-    <col width="22" customWidth="1" style="2" min="9" max="9"/>
-    <col width="15" customWidth="1" style="2" min="10" max="10"/>
+    <col width="12" customWidth="1" style="5" min="2" max="2"/>
+    <col width="10.4" customWidth="1" style="5" min="3" max="3"/>
+    <col width="9.630000000000001" customWidth="1" style="5" min="4" max="4"/>
+    <col width="10.06" customWidth="1" style="5" min="5" max="5"/>
+    <col width="16.31" customWidth="1" style="5" min="6" max="6"/>
+    <col width="16.14" customWidth="1" style="5" min="7" max="7"/>
+    <col width="19.79" customWidth="1" style="5" min="8" max="8"/>
+    <col width="22" customWidth="1" style="5" min="9" max="9"/>
+    <col width="15" customWidth="1" style="5" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="3">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Mã đơn</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Loại hàng</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Nơi gửi</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Nơi nhận</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Khối lượng (kg)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Loại vận chuyển</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Cước cơ bản (đ/kg)</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Phí vận chuyển (đ)</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="3">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Phân loại cước</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="6">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>DH001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Khách 4</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="5" t="n">
         <v>20.7</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="9" t="n">
         <v>186300</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="6">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>DH002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Khách 3</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="5" t="n">
         <v>42.7</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="9" t="n">
         <v>384300</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="3">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="6">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>DH003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Khách 9</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="5" t="n">
         <v>12.6</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="9" t="n">
         <v>119700</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="3">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="6">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>DH004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Khách 28</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I5" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="3">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>DH005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Khách 29</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="5" t="n">
         <v>33.5</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="9" t="n">
         <v>301500</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="3">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="6">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>DH006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Khách 2</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="5" t="n">
         <v>24.1</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I7" s="9" t="n">
         <v>325350</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="3">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="6">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>DH007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Khách 3</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="5" t="n">
         <v>40.2</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="9" t="n">
         <v>361800</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="3">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="6">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>DH008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Khách 39</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="5" t="n">
         <v>20.2</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>383600</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>364420</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="3">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="6">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>DH009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Khách 33</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="5" t="n">
         <v>33.6</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I10" s="9" t="n">
         <v>453600</v>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="3">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="6">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>DH010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Khách 33</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="5" t="n">
         <v>41.1</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I11" s="9" t="n">
         <v>554850</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="3">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="6">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>DH011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Khách 43</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I12" s="9" t="n">
         <v>245100</v>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="3">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="6">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>DH012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Khách 5</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="5" t="n">
         <v>28.9</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n">
-        <v>390150</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H13" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>370642.5</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="3">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="6">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>DH013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Khách 2</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="5" t="n">
         <v>31.6</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="9" t="n">
         <v>284400</v>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="3">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="6">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>DH014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Khách 23</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="5" t="n">
         <v>25.3</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="9" t="n">
         <v>227700</v>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="3">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="6">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>DH015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Khách 41</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="5" t="n">
         <v>31.7</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="9" t="n">
         <v>285300</v>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="3">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="6">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>DH016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Khách 35</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="5" t="n">
         <v>49.6</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H17" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I17" s="9" t="n">
         <v>669600</v>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="3">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="6">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>DH017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Khách 25</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="5" t="n">
         <v>7.2</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I18" s="9" t="n">
         <v>68400</v>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="3">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="6">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>DH018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Khách 2</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I19" s="9" t="n">
         <v>199500</v>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="3">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="6">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>DH019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Khách 41</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="5" t="n">
         <v>31.1</v>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H20" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I20" s="9" t="n">
         <v>579800</v>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="3">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="6">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>DH020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Khách 23</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="5" t="n">
         <v>21.9</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I21" s="9" t="n">
         <v>197100</v>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="3">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="6">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>DH021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Khách 35</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="5" t="n">
         <v>34.9</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I22" s="9" t="n">
         <v>471150</v>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="3">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="6">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>DH022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Khách 2</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I23" s="9" t="n">
         <v>62000</v>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="3">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="24" ht="15" customHeight="1" s="6">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>DH023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Khách 22</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="5" t="n">
         <v>32.1</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
-        <v>288900</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="H24" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>274455</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="3">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="6">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>DH024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Khách 27</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="5" t="n">
         <v>33.6</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H25" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I25" s="9" t="n">
         <v>624800</v>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="3">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="6">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>DH025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Khách 6</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="5" t="n">
         <v>26.2</v>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H26" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I26" s="9" t="n">
         <v>491600</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="3">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="27" ht="15" customHeight="1" s="6">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>DH026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Khách 20</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="5" t="n">
         <v>41.9</v>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H27" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I27" s="9" t="n">
         <v>565650</v>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="3">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="6">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>DH027</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Khách 9</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="5" t="n">
         <v>6.4</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H28" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I28" s="9" t="n">
         <v>60800</v>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="3">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="6">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>DH028</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Khách 38</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="5" t="n">
         <v>37.2</v>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I29" s="9" t="n">
         <v>502200.0000000001</v>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="3">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="30" ht="15" customHeight="1" s="6">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>DH029</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Khách 43</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="5" t="n">
         <v>43.6</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I30" s="9" t="n">
         <v>804800</v>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="3">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="31" ht="15" customHeight="1" s="6">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>DH030</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Khách 47</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="5" t="n">
         <v>21.7</v>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H31" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I31" s="9" t="n">
         <v>195300</v>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="3">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="6">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>DH031</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Khách 11</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="5" t="n">
         <v>26.1</v>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I32" s="9" t="n">
         <v>489800</v>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="3">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="33" ht="15" customHeight="1" s="6">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>DH032</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Khách 9</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" s="5" t="n">
         <v>36.5</v>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I33" s="9" t="n">
         <v>328500</v>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="3">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="6">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>DH033</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Khách 37</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" s="5" t="n">
         <v>46.5</v>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H34" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I34" s="9" t="n">
         <v>418500</v>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="3">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="6">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>DH034</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Khách 14</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H35" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I35" s="9" t="n">
         <v>72000</v>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="3">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="6">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>DH035</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Khách 6</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" s="5" t="n">
         <v>49.8</v>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="H36" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I36" s="9" t="n">
         <v>448200</v>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="3">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="6">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>DH036</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Khách 13</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="5" t="n">
         <v>30.2</v>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I37" s="9" t="n">
         <v>271800</v>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="3">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="38" ht="15" customHeight="1" s="6">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>DH037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Khách 22</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="H38" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I38" s="9" t="n">
         <v>421200</v>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="3">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="39" ht="15" customHeight="1" s="6">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>DH038</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Khách 31</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H39" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I39" s="9" t="n">
         <v>58000</v>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="3">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="40" ht="15" customHeight="1" s="6">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>DH039</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Khách 37</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F40" s="5" t="n">
         <v>45.8</v>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="H40" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I40" s="9" t="n">
         <v>844400</v>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="3">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="41" ht="15" customHeight="1" s="6">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>DH040</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Khách 9</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F41" s="5" t="n">
         <v>39.6</v>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I41" s="9" t="n">
         <v>732800</v>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="3">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="42" ht="15" customHeight="1" s="6">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>DH041</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Khách 32</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H42" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I42" s="9" t="n">
         <v>46500</v>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="3">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="43" ht="15" customHeight="1" s="6">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>DH042</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Khách 24</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F43" s="5" t="n">
         <v>18.3</v>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="H43" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I43" s="9" t="n">
         <v>260775</v>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="3">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="44" ht="15" customHeight="1" s="6">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>DH043</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Khách 22</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F44" s="5" t="n">
         <v>48.9</v>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="H44" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I44" s="9" t="n">
         <v>440100</v>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="3">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="45" ht="15" customHeight="1" s="6">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>DH044</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Khách 27</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F45" s="5" t="n">
         <v>46.3</v>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="H45" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I45" s="9" t="n">
         <v>853400</v>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="3">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="46" ht="15" customHeight="1" s="6">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>DH045</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Khách 25</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F46" s="5" t="n">
         <v>6.6</v>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H46" s="5" t="n">
+      <c r="H46" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I46" s="9" t="n">
         <v>94050</v>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="3">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="47" ht="15" customHeight="1" s="6">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>DH046</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Khách 33</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F47" s="5" t="n">
         <v>47.2</v>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H47" s="5" t="n">
-        <v>424800</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="H47" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I47" s="9" t="n">
+        <v>403560</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="3">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="48" ht="15" customHeight="1" s="6">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>DH047</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Khách 38</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H48" s="5" t="n">
+      <c r="H48" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I48" s="9" t="n">
         <v>443000</v>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="3">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="49" ht="15" customHeight="1" s="6">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>DH048</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Khách 21</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="H49" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I49" s="9" t="n">
         <v>777800</v>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="3">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="50" ht="15" customHeight="1" s="6">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>DH049</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Khách 37</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H50" s="5" t="n">
+      <c r="H50" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I50" s="9" t="n">
         <v>434000</v>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="3">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="51" ht="15" customHeight="1" s="6">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>DH050</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Khách 18</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F51" s="5" t="n">
         <v>6.6</v>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H51" s="5" t="n">
+      <c r="H51" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I51" s="9" t="n">
         <v>94050</v>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="3">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="52" ht="15" customHeight="1" s="6">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>DH051</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Khách 43</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H52" s="5" t="n">
+      <c r="H52" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I52" s="9" t="n">
         <v>364500</v>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="3">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="53" ht="15" customHeight="1" s="6">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>DH052</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Khách 35</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" s="5" t="n">
         <v>18.8</v>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H53" s="5" t="n">
+      <c r="H53" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I53" s="9" t="n">
         <v>178600</v>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="3">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="54" ht="15" customHeight="1" s="6">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>DH053</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Khách 39</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F54" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H54" s="5" t="n">
+      <c r="H54" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I54" s="9" t="n">
         <v>830000</v>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="3">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="55" ht="15" customHeight="1" s="6">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>DH054</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Khách 50</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H55" s="5" t="n">
+      <c r="H55" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I55" s="9" t="n">
         <v>329400</v>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="3">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="56" ht="15" customHeight="1" s="6">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>DH055</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>Khách 45</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H56" s="5" t="n">
-        <v>125400</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="H56" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I56" s="9" t="n">
+        <v>119130</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="3">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="57" ht="15" customHeight="1" s="6">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>DH056</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Khách 23</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F57" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H57" s="5" t="n">
+      <c r="H57" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I57" s="9" t="n">
         <v>42000</v>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="3">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="58" ht="15" customHeight="1" s="6">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>DH057</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>Khách 11</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="F58" s="5" t="n">
         <v>26.5</v>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H58" s="5" t="n">
+      <c r="H58" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I58" s="9" t="n">
         <v>497000</v>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="3">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="59" ht="15" customHeight="1" s="6">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>DH058</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Khách 34</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F59" s="5" t="n">
         <v>43.4</v>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H59" s="5" t="n">
+      <c r="H59" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I59" s="9" t="n">
         <v>585900</v>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="3">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="60" ht="15" customHeight="1" s="6">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>DH059</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Khách 15</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="F60" s="5" t="n">
         <v>22.4</v>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H60" s="5" t="n">
+      <c r="H60" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I60" s="9" t="n">
         <v>423200</v>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="3">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="61" ht="15" customHeight="1" s="6">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>DH060</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Khách 36</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F61" s="5" t="n">
         <v>47.1</v>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H61" s="5" t="n">
+      <c r="H61" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I61" s="9" t="n">
         <v>423900</v>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="3">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="62" ht="15" customHeight="1" s="6">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>DH061</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Khách 41</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" s="5" t="n">
         <v>39.7</v>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H62" s="5" t="n">
+      <c r="H62" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I62" s="9" t="n">
         <v>357300</v>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="3">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="63" ht="15" customHeight="1" s="6">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>DH062</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>Khách 4</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F63" s="5" t="n">
         <v>32.9</v>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H63" s="5" t="n">
+      <c r="H63" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I63" s="9" t="n">
         <v>612200</v>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="3">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="64" ht="15" customHeight="1" s="6">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>DH063</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Khách 23</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F64" s="5" t="n">
         <v>10.1</v>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H64" s="5" t="n">
-        <v>95950</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="H64" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I64" s="9" t="n">
+        <v>91152.5</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="3">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="65" ht="15" customHeight="1" s="6">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>DH064</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Khách 16</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H65" s="5" t="n">
-        <v>41000</v>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="H65" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I65" s="9" t="n">
+        <v>38950</v>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="3">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="66" ht="15" customHeight="1" s="6">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>DH065</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Khách 1</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H66" s="5" t="n">
+      <c r="H66" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I66" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="3">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="67" ht="15" customHeight="1" s="6">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>DH066</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Khách 47</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="F67" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H67" s="5" t="n">
+      <c r="H67" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I67" s="9" t="n">
         <v>222300</v>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="3">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="68" ht="15" customHeight="1" s="6">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>DH067</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Khách 43</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="F68" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H68" s="5" t="n">
+      <c r="H68" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I68" s="9" t="n">
         <v>488000</v>
       </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="3">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="69" ht="15" customHeight="1" s="6">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>DH068</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Khách 24</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="F69" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H69" s="5" t="n">
-        <v>398000</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="H69" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I69" s="9" t="n">
+        <v>378100</v>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="3">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="70" ht="15" customHeight="1" s="6">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>DH069</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Khách 43</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="F70" s="5" t="n">
         <v>9.9</v>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H70" s="5" t="n">
+      <c r="H70" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I70" s="9" t="n">
         <v>94050</v>
       </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="3">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="71" ht="15" customHeight="1" s="6">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>DH070</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Khách 32</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="F71" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H71" s="5" t="n">
+      <c r="H71" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I71" s="9" t="n">
         <v>452000</v>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="3">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="72" ht="15" customHeight="1" s="6">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>DH071</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>Khách 7</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="F72" s="5" t="n">
         <v>46.4</v>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H72" s="5" t="n">
-        <v>626400</v>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="H72" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I72" s="9" t="n">
+        <v>595080</v>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="3">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="73" ht="15" customHeight="1" s="6">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>DH072</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Khách 36</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="F73" s="5" t="n">
         <v>26.3</v>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H73" s="5" t="n">
+      <c r="H73" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I73" s="9" t="n">
         <v>355050</v>
       </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="3">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="74" ht="15" customHeight="1" s="6">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>DH073</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>Khách 24</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="F74" s="5" t="n">
         <v>5.7</v>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H74" s="5" t="n">
+      <c r="H74" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I74" s="9" t="n">
         <v>54150</v>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="3">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="75" ht="15" customHeight="1" s="6">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>DH074</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Khách 38</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="F75" s="5" t="n">
         <v>4.6</v>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H75" s="5" t="n">
+      <c r="H75" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I75" s="9" t="n">
         <v>112000</v>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="3">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="76" ht="15" customHeight="1" s="6">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>DH075</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>Khách 14</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F76" s="5" t="n">
         <v>6.7</v>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H76" s="5" t="n">
+      <c r="H76" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I76" s="9" t="n">
         <v>95475</v>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="3">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="77" ht="15" customHeight="1" s="6">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>DH076</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>Khách 9</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="F77" s="5" t="n">
         <v>39.8</v>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H77" s="5" t="n">
+      <c r="H77" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I77" s="9" t="n">
         <v>537300</v>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="3">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="78" ht="15" customHeight="1" s="6">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>DH077</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>Khách 3</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="F78" s="5" t="n">
         <v>23.2</v>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H78" s="5" t="n">
+      <c r="H78" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I78" s="9" t="n">
         <v>208800</v>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="3">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="79" ht="15" customHeight="1" s="6">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>DH078</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>Khách 43</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="F79" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H79" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I79" s="9" t="n">
         <v>114000</v>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="3">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="80" ht="15" customHeight="1" s="6">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>DH079</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>Khách 45</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="F80" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H80" s="5" t="n">
+      <c r="H80" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I80" s="9" t="n">
         <v>37500</v>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="3">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="81" ht="15" customHeight="1" s="6">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>DH080</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>Khách 14</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="F81" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H81" s="5" t="n">
+      <c r="H81" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I81" s="9" t="n">
         <v>412400</v>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="3">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="82" ht="15" customHeight="1" s="6">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>DH081</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>Khách 10</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F82" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H82" s="5" t="n">
+      <c r="H82" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I82" s="9" t="n">
         <v>237975</v>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="3">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="83" ht="15" customHeight="1" s="6">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>DH082</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>Khách 23</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="F83" s="5" t="n">
         <v>27.7</v>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H83" s="5" t="n">
+      <c r="H83" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I83" s="9" t="n">
         <v>249300</v>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="J83" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="3">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="84" ht="15" customHeight="1" s="6">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>DH083</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>Khách 16</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="F84" s="5" t="n">
         <v>28.1</v>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H84" s="5" t="n">
-        <v>252900</v>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="H84" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I84" s="9" t="n">
+        <v>240255</v>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="3">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="85" ht="15" customHeight="1" s="6">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>DH084</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>Khách 39</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="F85" s="5" t="n">
         <v>48.8</v>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H85" s="5" t="n">
+      <c r="H85" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I85" s="9" t="n">
         <v>898400</v>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="3">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="86" ht="15" customHeight="1" s="6">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>DH085</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>Khách 24</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="F86" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H86" s="5" t="n">
+      <c r="H86" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I86" s="9" t="n">
         <v>189900</v>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="3">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="87" ht="15" customHeight="1" s="6">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>DH086</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Khách 39</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>Thời trang</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="F87" s="5" t="n">
         <v>34.7</v>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H87" s="5" t="n">
+      <c r="H87" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I87" s="9" t="n">
         <v>312300</v>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="3">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="88" ht="15" customHeight="1" s="6">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>DH087</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>Khách 23</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>Hà Nội</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="F88" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H88" s="5" t="n">
-        <v>215175</v>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="H88" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I88" s="9" t="n">
+        <v>204416.25</v>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1" s="3">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="89" ht="15" customHeight="1" s="6">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>DH088</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>Khách 47</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="F89" s="5" t="n">
         <v>43.1</v>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H89" s="5" t="n">
+      <c r="H89" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I89" s="9" t="n">
         <v>795800</v>
       </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="3">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="90" ht="15" customHeight="1" s="6">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>DH089</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>Khách 39</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="F90" s="5" t="n">
         <v>31.9</v>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H90" s="5" t="n">
-        <v>287100</v>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="H90" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I90" s="9" t="n">
+        <v>272745</v>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1" s="3">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="91" ht="15" customHeight="1" s="6">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>DH090</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>Khách 13</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>Hải Phòng</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E91" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="F91" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H91" s="5" t="n">
+      <c r="H91" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I91" s="9" t="n">
         <v>526500</v>
       </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="J91" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1" s="3">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="92" ht="15" customHeight="1" s="6">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>DH091</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>Khách 42</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="F92" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H92" s="5" t="n">
+      <c r="H92" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I92" s="9" t="n">
         <v>56000</v>
       </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1" s="3">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="93" ht="15" customHeight="1" s="6">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>DH092</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>Khách 2</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F93" s="2" t="n">
+      <c r="F93" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H93" s="5" t="n">
+      <c r="H93" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I93" s="9" t="n">
         <v>95000</v>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="15" customHeight="1" s="3">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="94" ht="15" customHeight="1" s="6">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>DH093</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>Khách 7</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>Thực phẩm</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F94" s="2" t="n">
+      <c r="F94" s="5" t="n">
         <v>6.5</v>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H94" s="5" t="n">
+      <c r="H94" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I94" s="9" t="n">
         <v>61750</v>
       </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="15" customHeight="1" s="3">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="95" ht="15" customHeight="1" s="6">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>DH094</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>Khách 24</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F95" s="2" t="n">
+      <c r="F95" s="5" t="n">
         <v>6.9</v>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H95" s="5" t="n">
-        <v>98325</v>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="H95" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I95" s="9" t="n">
+        <v>93408.75</v>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="3">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="96" ht="15" customHeight="1" s="6">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>DH095</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>Khách 6</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>Vũng Tàu</t>
         </is>
       </c>
-      <c r="F96" s="2" t="n">
+      <c r="F96" s="5" t="n">
         <v>39.7</v>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H96" s="5" t="n">
+      <c r="H96" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I96" s="9" t="n">
         <v>357300</v>
       </c>
-      <c r="I96" s="2" t="inlineStr">
+      <c r="J96" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="15" customHeight="1" s="3">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="97" ht="15" customHeight="1" s="6">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>DH096</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>Khách 43</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>Sách</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="F97" s="2" t="n">
+      <c r="F97" s="5" t="n">
         <v>14.7</v>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>Siêu tốc</t>
         </is>
       </c>
-      <c r="H97" s="5" t="n">
+      <c r="H97" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I97" s="9" t="n">
         <v>299300</v>
       </c>
-      <c r="I97" s="2" t="inlineStr">
+      <c r="J97" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="15" customHeight="1" s="3">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="98" ht="15" customHeight="1" s="6">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>DH097</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>Khách 49</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="F98" s="2" t="n">
+      <c r="F98" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>Tiêu chuẩn</t>
         </is>
       </c>
-      <c r="H98" s="5" t="n">
+      <c r="H98" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I98" s="9" t="n">
         <v>431100</v>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="J98" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="15" customHeight="1" s="3">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="99" ht="15" customHeight="1" s="6">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>DH098</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Khách 6</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>Điện tử</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F99" s="2" t="n">
+      <c r="F99" s="5" t="n">
         <v>22.3</v>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H99" s="5" t="n">
+      <c r="H99" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I99" s="9" t="n">
         <v>301050</v>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="J99" s="5" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" s="3">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="100" ht="15" customHeight="1" s="6">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>DH099</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>Khách 23</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>Mỹ phẩm</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>Đà Nẵng</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>Nha Trang</t>
         </is>
       </c>
-      <c r="F100" s="2" t="n">
+      <c r="F100" s="5" t="n">
         <v>45.3</v>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H100" s="5" t="n">
+      <c r="H100" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I100" s="9" t="n">
         <v>611550</v>
       </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="J100" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="3">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="101" ht="15" customHeight="1" s="6">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>DH100</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Khách 1</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>Gia dụng</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>Cần Thơ</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>TP.HCM</t>
         </is>
       </c>
-      <c r="F101" s="2" t="n">
+      <c r="F101" s="5" t="n">
         <v>45.8</v>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>Nhanh</t>
         </is>
       </c>
-      <c r="H101" s="5" t="n">
-        <v>618300</v>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="H101" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I101" s="9" t="n">
+        <v>587385</v>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
@@ -4796,85 +5114,85 @@
   <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.43359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="3">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Đề bài</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="3">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="6">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>BÀI TẬP OPENPYXL: TÍNH PHÍ VẬN CHUYỂN</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="3">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="6">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Yêu cầu:</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="3">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="6">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>1. Đọc sheet 'Dữ liệu' và tính cột 'Phí vận chuyển (đ)' theo điều kiện sau:</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="3">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Nếu Khối lượng &lt;= 5kg: Phí = Khối lượng * Cước cơ bản</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="3">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="6">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Nếu 5 &lt; Khối lượng &lt;= 20kg: Phí = Khối lượng * Cước cơ bản * 0.95 (giảm 5%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="3">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="6">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Nếu Khối lượng &gt; 20kg: Phí = Khối lượng * Cước cơ bản * 0.9 (giảm 10%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="3">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="6">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2. Nếu Loại vận chuyển là 'Siêu tốc' thì cộng thêm 20.000đ.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="3">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="6">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>3. Nếu Nơi gửi và Nơi nhận cùng miền (Bắc, Trung, Nam) thì giảm thêm 5%.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="3">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="6">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Gợi ý mở rộng:</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="3">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="6">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>- Tạo thêm cột 'Miền gửi', 'Miền nhận' dựa vào tỉnh/thành.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="3">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="6">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>- Tính tổng doanh thu, số đơn trên mỗi loại vận chuyển.</t>
         </is>
